--- a/doc/digital_tutor_roguelike_db_schema_v0_5.xlsx
+++ b/doc/digital_tutor_roguelike_db_schema_v0_5.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" r:id="Re51c160dc63d49fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admins" sheetId="2" r:id="R1249f49dae8b4936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Players" sheetId="3" r:id="R49be767c22bf4726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerData" sheetId="4" r:id="Ra89262577beb485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="5" r:id="R5be3ebe77f5146ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" r:id="R1cf3bf38c070426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnswerLogs" sheetId="7" r:id="R33f18d87da4549e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="8" r:id="Rccffadcf7dc84384"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterGroups" sheetId="9" r:id="R30eb33cad6ee4052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monsters" sheetId="10" r:id="R82b26e016ca94bff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterAI" sheetId="11" r:id="R22da0050f9914037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="12" r:id="R8073fb4f2a1e414c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effects" sheetId="13" r:id="R7b1ec8794693442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="14" r:id="Rfeaf89c21690459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rewards" sheetId="15" r:id="R633c81fe70534d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardGroups" sheetId="16" r:id="Rf175d4be034241c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleLogs" sheetId="17" r:id="R681d108e11a34a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" r:id="Rcfb6ae3c06274fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admins" sheetId="2" r:id="Ra590201857fb423d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Players" sheetId="3" r:id="R84f24a6d3ca04843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerData" sheetId="4" r:id="Raf244e9afcad4f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="5" r:id="R62d6efffd3cf46e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" r:id="Rde90f720fa184bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnswerLogs" sheetId="7" r:id="R7108ed4d0e884d76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stages" sheetId="8" r:id="R1889723b97af4133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterGroups" sheetId="9" r:id="Rf8979ecef20d40d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monsters" sheetId="10" r:id="Re1f22e95fc784b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterAI" sheetId="11" r:id="Ra1678b7fec054955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="12" r:id="R6dc89528f87941cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effects" sheetId="13" r:id="R7759cd8a9d194ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Items" sheetId="14" r:id="R230f62bf07384bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rewards" sheetId="15" r:id="R276d614ac7c447ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardGroups" sheetId="16" r:id="R80b5c726f81d4ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleLogs" sheetId="17" r:id="R1ecf2a918956455d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -283,7 +283,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="89">
+  <x:cellXfs count="90">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -591,6 +591,7 @@
     <x:xf numFmtId="203" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -987,6 +988,23 @@
         <x:v>46204.158348287034</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>gameEnabled</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Whether students can start the game.</x:v>
+      </x:c>
+      <x:c r="E11" s="89" t="n">
+        <x:v>46204.29190877315</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
